--- a/anexos/Estado de la cuestión Juan Calpa, Cristhian Padilla.xlsx
+++ b/anexos/Estado de la cuestión Juan Calpa, Cristhian Padilla.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repositorio\trabajo-de-grado-\anexos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cris\Documents\GitHub\trabajo-de-grado-\anexos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45A826D5-E7D5-4FC6-BCD8-A5BAA7B8209A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9427765F-59DE-4A27-875E-B474208275BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -658,7 +658,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -727,7 +727,13 @@
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Constantia"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
     </font>
   </fonts>
@@ -914,7 +920,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -943,54 +949,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1009,19 +967,55 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -29755,46 +29749,46 @@
       <c r="A1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="28"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="31"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="15"/>
     </row>
     <row r="3" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="28"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="12"/>
     </row>
     <row r="4" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="16" t="s">
         <v>26</v>
       </c>
       <c r="B4" s="5" t="s">
@@ -29809,26 +29803,26 @@
       <c r="E4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="18"/>
-      <c r="H4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="20"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="22"/>
+      <c r="A5" s="17"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E5" s="5"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="19"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="20"/>
     </row>
     <row r="6" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="16" t="s">
         <v>33</v>
       </c>
       <c r="B6" s="5" t="s">
@@ -29846,13 +29840,13 @@
       <c r="F6" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="23" t="s">
+      <c r="G6" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="19"/>
+      <c r="H6" s="20"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="22"/>
+      <c r="A7" s="17"/>
       <c r="B7" s="5"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -29860,67 +29854,67 @@
         <v>70</v>
       </c>
       <c r="F7" s="5"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="19"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="20"/>
     </row>
     <row r="8" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="28"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="12"/>
     </row>
     <row r="9" spans="1:8" ht="76.150000000000006" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="28"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="12"/>
     </row>
     <row r="10" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="28"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="12"/>
     </row>
     <row r="11" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="20"/>
     </row>
     <row r="12" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="16" t="s">
         <v>43</v>
       </c>
       <c r="B12" s="5" t="s">
@@ -29935,40 +29929,40 @@
       <c r="E12" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F12" s="23" t="s">
+      <c r="F12" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="18"/>
-      <c r="H12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="20"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="22"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="9" t="s">
         <v>70</v>
       </c>
       <c r="E13" s="5"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="19"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="20"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="25"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="24"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="16" t="s">
         <v>49</v>
       </c>
       <c r="B15" s="5" t="s">
@@ -29986,13 +29980,13 @@
       <c r="F15" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="G15" s="23" t="s">
+      <c r="G15" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="H15" s="19"/>
+      <c r="H15" s="20"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="22"/>
+      <c r="A16" s="17"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
       <c r="D16" s="8" t="s">
@@ -30000,67 +29994,67 @@
       </c>
       <c r="E16" s="8"/>
       <c r="F16" s="5"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="19"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="20"/>
     </row>
     <row r="17" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="28"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="12"/>
     </row>
     <row r="18" spans="1:8" ht="94.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="26" t="s">
+      <c r="B18" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="28"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="12"/>
     </row>
     <row r="19" spans="1:8" ht="51.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B19" s="26" t="s">
+      <c r="B19" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="28"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="12"/>
     </row>
     <row r="20" spans="1:8" ht="40.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B20" s="26" t="s">
+      <c r="B20" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="28"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="12"/>
     </row>
     <row r="21" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="16" t="s">
         <v>59</v>
       </c>
       <c r="B21" s="5" t="s">
@@ -30086,7 +30080,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="22"/>
+      <c r="A22" s="17"/>
       <c r="B22" s="8" t="s">
         <v>70</v>
       </c>
@@ -30101,15 +30095,426 @@
       <c r="A23" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="20"/>
+    </row>
+  </sheetData>
+  <mergeCells count="26">
+    <mergeCell ref="B23:H23"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="B19:H19"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="B9:H9"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="B23" r:id="rId1" xr:uid="{06A3115A-1DC9-4848-B29A-C321974DCA5A}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21B36836-EC2B-4038-9DC5-83A45552B604}">
+  <dimension ref="A1:H23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="21.5703125" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="5" max="5" width="17.85546875" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="12"/>
+    </row>
+    <row r="2" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="15"/>
+    </row>
+    <row r="3" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="12"/>
+    </row>
+    <row r="4" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="19"/>
+      <c r="H4" s="20"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="17"/>
+      <c r="B5" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="20"/>
+    </row>
+    <row r="6" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="20"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="17"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="20"/>
+    </row>
+    <row r="8" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="12"/>
+    </row>
+    <row r="9" spans="1:8" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="12"/>
+    </row>
+    <row r="10" spans="1:8" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="12"/>
+    </row>
+    <row r="11" spans="1:8" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="20"/>
+    </row>
+    <row r="12" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" s="19"/>
+      <c r="H12" s="20"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="17"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="20"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="24"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" s="20"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="17"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F16" s="5"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="20"/>
+    </row>
+    <row r="17" spans="1:8" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="12"/>
+    </row>
+    <row r="18" spans="1:8" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="12"/>
+    </row>
+    <row r="19" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="12"/>
+    </row>
+    <row r="20" spans="1:8" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="12"/>
+    </row>
+    <row r="21" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A21" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="17"/>
+      <c r="B22" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="5"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="8"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="26">
@@ -30141,14 +30546,15 @@
     <mergeCell ref="A21:A22"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B23" r:id="rId1" xr:uid="{06A3115A-1DC9-4848-B29A-C321974DCA5A}"/>
+    <hyperlink ref="B23" r:id="rId1" xr:uid="{958F6A29-6789-4A27-845C-AFD1EFDFEFD7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21B36836-EC2B-4038-9DC5-83A45552B604}">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25B573E4-84D2-47DC-9A23-D43656C826A8}">
   <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -30164,46 +30570,46 @@
       <c r="A1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="26" t="s">
-        <v>119</v>
+      <c r="B1" s="10" t="s">
+        <v>108</v>
       </c>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="28"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="29" t="s">
-        <v>120</v>
+      <c r="B2" s="13" t="s">
+        <v>109</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="31"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="15"/>
     </row>
     <row r="3" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="26" t="s">
-        <v>121</v>
+      <c r="B3" s="10" t="s">
+        <v>110</v>
       </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="28"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="12"/>
     </row>
     <row r="4" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="16" t="s">
         <v>26</v>
       </c>
       <c r="B4" s="5" t="s">
@@ -30218,26 +30624,26 @@
       <c r="E4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="18"/>
-      <c r="H4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="20"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="22"/>
-      <c r="B5" s="5" t="s">
+      <c r="A5" s="17"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="8"/>
       <c r="E5" s="5"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="19"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="20"/>
     </row>
     <row r="6" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="16" t="s">
         <v>33</v>
       </c>
       <c r="B6" s="5" t="s">
@@ -30255,83 +30661,81 @@
       <c r="F6" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="23" t="s">
+      <c r="G6" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="19"/>
+      <c r="H6" s="20"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="22"/>
+      <c r="A7" s="17"/>
       <c r="B7" s="5"/>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7" s="5"/>
       <c r="F7" s="5"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="19"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="20"/>
     </row>
     <row r="8" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="26" t="s">
-        <v>122</v>
+      <c r="B8" s="10" t="s">
+        <v>118</v>
       </c>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="28"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="12"/>
     </row>
     <row r="9" spans="1:8" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="26" t="s">
-        <v>125</v>
+      <c r="B9" s="10" t="s">
+        <v>111</v>
       </c>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="28"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="12"/>
     </row>
     <row r="10" spans="1:8" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="26" t="s">
-        <v>126</v>
+      <c r="B10" s="10" t="s">
+        <v>112</v>
       </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="28"/>
-    </row>
-    <row r="11" spans="1:8" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="12"/>
+    </row>
+    <row r="11" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="20" t="s">
-        <v>127</v>
+      <c r="B11" s="21" t="s">
+        <v>113</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="20"/>
     </row>
     <row r="12" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="16" t="s">
         <v>43</v>
       </c>
       <c r="B12" s="5" t="s">
@@ -30346,40 +30750,40 @@
       <c r="E12" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F12" s="23" t="s">
+      <c r="F12" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="18"/>
-      <c r="H12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="20"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="22"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="9" t="s">
+      <c r="C13" s="5" t="s">
         <v>70</v>
       </c>
+      <c r="D13" s="9"/>
       <c r="E13" s="5"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="19"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="20"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="20" t="s">
-        <v>122</v>
+      <c r="B14" s="21" t="s">
+        <v>118</v>
       </c>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="25"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="24"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="16" t="s">
         <v>49</v>
       </c>
       <c r="B15" s="5" t="s">
@@ -30397,81 +30801,81 @@
       <c r="F15" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="G15" s="23" t="s">
+      <c r="G15" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="H15" s="19"/>
+      <c r="H15" s="20"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="22"/>
+      <c r="A16" s="17"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
       <c r="D16" s="8"/>
-      <c r="E16" s="8" t="s">
-        <v>70</v>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="21" t="s">
+        <v>101</v>
       </c>
-      <c r="F16" s="5"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="19"/>
-    </row>
-    <row r="17" spans="1:8" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="8" t="s">
+      <c r="H16" s="20"/>
+    </row>
+    <row r="17" spans="1:8" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B17" s="26" t="s">
-        <v>128</v>
+      <c r="B17" s="10" t="s">
+        <v>114</v>
       </c>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="28"/>
-    </row>
-    <row r="18" spans="1:8" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="12"/>
+    </row>
+    <row r="18" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="26" t="s">
-        <v>129</v>
+      <c r="B18" s="10" t="s">
+        <v>115</v>
       </c>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="28"/>
-    </row>
-    <row r="19" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="12"/>
+    </row>
+    <row r="19" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B19" s="26" t="s">
-        <v>145</v>
+      <c r="B19" s="10" t="s">
+        <v>144</v>
       </c>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="28"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="12"/>
     </row>
     <row r="20" spans="1:8" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B20" s="26" t="s">
-        <v>123</v>
+      <c r="B20" s="10" t="s">
+        <v>117</v>
       </c>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="28"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="12"/>
     </row>
     <row r="21" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="16" t="s">
         <v>59</v>
       </c>
       <c r="B21" s="5" t="s">
@@ -30497,7 +30901,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="22"/>
+      <c r="A22" s="17"/>
       <c r="B22" s="8" t="s">
         <v>70</v>
       </c>
@@ -30512,15 +30916,15 @@
       <c r="A23" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B23" s="17" t="s">
-        <v>124</v>
+      <c r="B23" s="22" t="s">
+        <v>116</v>
       </c>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="26">
@@ -30552,70 +30956,71 @@
     <mergeCell ref="B9:H9"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B23" r:id="rId1" xr:uid="{958F6A29-6789-4A27-845C-AFD1EFDFEFD7}"/>
+    <hyperlink ref="B23" r:id="rId1" xr:uid="{D6663CD1-BA9E-44A4-8B92-139F79375522}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25B573E4-84D2-47DC-9A23-D43656C826A8}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35E73F9C-3195-437F-844E-917B5A940578}">
   <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.5703125" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="8" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="26" t="s">
-        <v>108</v>
+      <c r="B1" s="10" t="s">
+        <v>93</v>
       </c>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="28"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="29" t="s">
-        <v>109</v>
+      <c r="B2" s="13" t="s">
+        <v>94</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="31"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="15"/>
     </row>
     <row r="3" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="26" t="s">
-        <v>110</v>
+      <c r="B3" s="10" t="s">
+        <v>95</v>
       </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="28"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="12"/>
     </row>
     <row r="4" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="16" t="s">
         <v>26</v>
       </c>
       <c r="B4" s="5" t="s">
@@ -30630,26 +31035,28 @@
       <c r="E4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="18"/>
-      <c r="H4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="20"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="22"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="8" t="s">
+      <c r="A5" s="17"/>
+      <c r="B5" s="5" t="s">
         <v>70</v>
       </c>
+      <c r="C5" s="5"/>
+      <c r="D5" s="8"/>
       <c r="E5" s="5"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="19"/>
+      <c r="F5" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="G5" s="19"/>
+      <c r="H5" s="20"/>
     </row>
     <row r="6" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="16" t="s">
         <v>33</v>
       </c>
       <c r="B6" s="5" t="s">
@@ -30667,81 +31074,81 @@
       <c r="F6" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="23" t="s">
+      <c r="G6" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="19"/>
+      <c r="H6" s="20"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="22"/>
+      <c r="A7" s="17"/>
       <c r="B7" s="5"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="5" t="s">
+      <c r="C7" s="8" t="s">
         <v>70</v>
       </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="5"/>
       <c r="F7" s="5"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="19"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="20"/>
     </row>
     <row r="8" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="26" t="s">
-        <v>118</v>
+      <c r="B8" s="10" t="s">
+        <v>96</v>
       </c>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="28"/>
-    </row>
-    <row r="9" spans="1:8" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="12"/>
+    </row>
+    <row r="9" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="26" t="s">
-        <v>111</v>
+      <c r="B9" s="10" t="s">
+        <v>97</v>
       </c>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="28"/>
-    </row>
-    <row r="10" spans="1:8" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="12"/>
+    </row>
+    <row r="10" spans="1:8" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="26" t="s">
-        <v>112</v>
+      <c r="B10" s="10" t="s">
+        <v>98</v>
       </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="28"/>
-    </row>
-    <row r="11" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="12"/>
+    </row>
+    <row r="11" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="20" t="s">
-        <v>113</v>
+      <c r="B11" s="21" t="s">
+        <v>99</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="20"/>
     </row>
     <row r="12" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="16" t="s">
         <v>43</v>
       </c>
       <c r="B12" s="5" t="s">
@@ -30756,40 +31163,40 @@
       <c r="E12" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F12" s="23" t="s">
+      <c r="F12" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="18"/>
-      <c r="H12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="20"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="22"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="5"/>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="5"/>
+      <c r="D13" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="D13" s="9"/>
       <c r="E13" s="5"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="19"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="20"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="20" t="s">
-        <v>118</v>
+      <c r="B14" s="21" t="s">
+        <v>100</v>
       </c>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="25"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="24"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="16" t="s">
         <v>49</v>
       </c>
       <c r="B15" s="5" t="s">
@@ -30807,81 +31214,81 @@
       <c r="F15" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="G15" s="23" t="s">
+      <c r="G15" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="H15" s="19"/>
+      <c r="H15" s="20"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="22"/>
+      <c r="A16" s="17"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
       <c r="D16" s="8"/>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
-      <c r="G16" s="20" t="s">
+      <c r="G16" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="H16" s="19"/>
-    </row>
-    <row r="17" spans="1:8" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H16" s="20"/>
+    </row>
+    <row r="17" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B17" s="26" t="s">
-        <v>114</v>
+      <c r="B17" s="10" t="s">
+        <v>102</v>
       </c>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="28"/>
-    </row>
-    <row r="18" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="12"/>
+    </row>
+    <row r="18" spans="1:8" ht="108.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="26" t="s">
-        <v>115</v>
+      <c r="B18" s="10" t="s">
+        <v>103</v>
       </c>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="28"/>
-    </row>
-    <row r="19" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="12"/>
+    </row>
+    <row r="19" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B19" s="26" t="s">
-        <v>144</v>
+      <c r="B19" s="10" t="s">
+        <v>143</v>
       </c>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="28"/>
-    </row>
-    <row r="20" spans="1:8" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="12"/>
+    </row>
+    <row r="20" spans="1:8" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B20" s="26" t="s">
-        <v>117</v>
+      <c r="B20" s="10" t="s">
+        <v>104</v>
       </c>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="28"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="12"/>
     </row>
     <row r="21" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="16" t="s">
         <v>59</v>
       </c>
       <c r="B21" s="5" t="s">
@@ -30907,12 +31314,12 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="22"/>
-      <c r="B22" s="8" t="s">
+      <c r="A22" s="17"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="8"/>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
@@ -30922,15 +31329,15 @@
       <c r="A23" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B23" s="17" t="s">
-        <v>116</v>
+      <c r="B23" s="22" t="s">
+        <v>105</v>
       </c>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="26">
@@ -30962,419 +31369,6 @@
     <mergeCell ref="A21:A22"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B23" r:id="rId1" xr:uid="{D6663CD1-BA9E-44A4-8B92-139F79375522}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35E73F9C-3195-437F-844E-917B5A940578}">
-  <dimension ref="A1:H23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.28515625" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="8" width="15.28515625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="28"/>
-    </row>
-    <row r="2" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="29" t="s">
-        <v>94</v>
-      </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="31"/>
-    </row>
-    <row r="3" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="28"/>
-    </row>
-    <row r="4" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="18"/>
-      <c r="H4" s="19"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="22"/>
-      <c r="B5" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="G5" s="18"/>
-      <c r="H5" s="19"/>
-    </row>
-    <row r="6" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" s="19"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="22"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="19"/>
-    </row>
-    <row r="8" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>96</v>
-      </c>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="28"/>
-    </row>
-    <row r="9" spans="1:8" ht="51" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="28"/>
-    </row>
-    <row r="10" spans="1:8" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="28"/>
-    </row>
-    <row r="11" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B11" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="19"/>
-    </row>
-    <row r="12" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A12" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F12" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="G12" s="18"/>
-      <c r="H12" s="19"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="22"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="19"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="25"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="G15" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="H15" s="19"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="22"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="H16" s="19"/>
-    </row>
-    <row r="17" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B17" s="26" t="s">
-        <v>102</v>
-      </c>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="28"/>
-    </row>
-    <row r="18" spans="1:8" ht="108.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B18" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="28"/>
-    </row>
-    <row r="19" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B19" s="26" t="s">
-        <v>143</v>
-      </c>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="28"/>
-    </row>
-    <row r="20" spans="1:8" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B20" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="28"/>
-    </row>
-    <row r="21" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A21" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="22"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="8"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="19"/>
-    </row>
-  </sheetData>
-  <mergeCells count="26">
-    <mergeCell ref="B23:H23"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="B17:H17"/>
-    <mergeCell ref="B18:H18"/>
-    <mergeCell ref="B19:H19"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="B10:H10"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="B9:H9"/>
-  </mergeCells>
-  <hyperlinks>
     <hyperlink ref="B23" r:id="rId1" xr:uid="{2C7E88CD-4F29-477C-8053-58AE35A9B153}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -31400,46 +31394,46 @@
       <c r="A1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="28"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="31"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="15"/>
     </row>
     <row r="3" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="28"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="12"/>
     </row>
     <row r="4" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="16" t="s">
         <v>26</v>
       </c>
       <c r="B4" s="5" t="s">
@@ -31454,26 +31448,26 @@
       <c r="E4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="18"/>
-      <c r="H4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="20"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="22"/>
+      <c r="A5" s="17"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E5" s="5"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="19"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="20"/>
     </row>
     <row r="6" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="16" t="s">
         <v>33</v>
       </c>
       <c r="B6" s="5" t="s">
@@ -31491,13 +31485,13 @@
       <c r="F6" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="23" t="s">
+      <c r="G6" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="19"/>
+      <c r="H6" s="20"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="22"/>
+      <c r="A7" s="17"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="8" t="s">
@@ -31505,67 +31499,67 @@
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="19"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="20"/>
     </row>
     <row r="8" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="28"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="12"/>
     </row>
     <row r="9" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="28"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="12"/>
     </row>
     <row r="10" spans="1:8" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="28"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="12"/>
     </row>
     <row r="11" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="20"/>
     </row>
     <row r="12" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="16" t="s">
         <v>43</v>
       </c>
       <c r="B12" s="5" t="s">
@@ -31580,40 +31574,40 @@
       <c r="E12" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F12" s="23" t="s">
+      <c r="F12" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="18"/>
-      <c r="H12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="20"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="22"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="9" t="s">
         <v>70</v>
       </c>
       <c r="E13" s="5"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="19"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="20"/>
     </row>
     <row r="14" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="25"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="24"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="16" t="s">
         <v>49</v>
       </c>
       <c r="B15" s="5" t="s">
@@ -31631,13 +31625,13 @@
       <c r="F15" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="G15" s="23" t="s">
+      <c r="G15" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="H15" s="19"/>
+      <c r="H15" s="20"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="22"/>
+      <c r="A16" s="17"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
       <c r="D16" s="8" t="s">
@@ -31645,67 +31639,67 @@
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="19"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="20"/>
     </row>
     <row r="17" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="28"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="12"/>
     </row>
     <row r="18" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="26" t="s">
+      <c r="B18" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="28"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="12"/>
     </row>
     <row r="19" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B19" s="26" t="s">
+      <c r="B19" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="28"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="12"/>
     </row>
     <row r="20" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B20" s="26" t="s">
+      <c r="B20" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="28"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="12"/>
     </row>
     <row r="21" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="16" t="s">
         <v>59</v>
       </c>
       <c r="B21" s="5" t="s">
@@ -31731,7 +31725,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A22" s="22"/>
+      <c r="A22" s="17"/>
       <c r="B22" s="8"/>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
@@ -31746,18 +31740,30 @@
       <c r="A23" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="B9:H9"/>
     <mergeCell ref="B23:H23"/>
     <mergeCell ref="B11:H11"/>
     <mergeCell ref="A12:A13"/>
@@ -31772,18 +31778,6 @@
     <mergeCell ref="B19:H19"/>
     <mergeCell ref="B20:H20"/>
     <mergeCell ref="A21:A22"/>
-    <mergeCell ref="B10:H10"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="B9:H9"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B23" r:id="rId1" xr:uid="{317E717B-A32B-4455-8F31-46AC4478125A}"/>
@@ -31812,15 +31806,15 @@
       <c r="A1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="28"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="12"/>
       <c r="I1" s="4"/>
       <c r="J1" s="4"/>
       <c r="K1" s="4"/>
@@ -31844,15 +31838,15 @@
       <c r="A2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="31"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="15"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
@@ -31876,15 +31870,15 @@
       <c r="A3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="28"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="12"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
@@ -31905,7 +31899,7 @@
       <c r="Z3" s="4"/>
     </row>
     <row r="4" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="16" t="s">
         <v>26</v>
       </c>
       <c r="B4" s="5" t="s">
@@ -31920,11 +31914,11 @@
       <c r="E4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="18"/>
-      <c r="H4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="20"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
@@ -31945,16 +31939,16 @@
       <c r="Z4" s="4"/>
     </row>
     <row r="5" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="22"/>
+      <c r="A5" s="17"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E5" s="5"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="19"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="20"/>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
@@ -31975,7 +31969,7 @@
       <c r="Z5" s="4"/>
     </row>
     <row r="6" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="16" t="s">
         <v>33</v>
       </c>
       <c r="B6" s="5" t="s">
@@ -31993,10 +31987,10 @@
       <c r="F6" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="23" t="s">
+      <c r="G6" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="19"/>
+      <c r="H6" s="20"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
@@ -32017,7 +32011,7 @@
       <c r="Z6" s="4"/>
     </row>
     <row r="7" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="22"/>
+      <c r="A7" s="17"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="8" t="s">
@@ -32025,8 +32019,8 @@
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="19"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="20"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
@@ -32050,15 +32044,15 @@
       <c r="A8" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="28"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="12"/>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
@@ -32082,15 +32076,15 @@
       <c r="A9" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="28"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="12"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
@@ -32114,15 +32108,15 @@
       <c r="A10" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="28"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="12"/>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
@@ -32145,15 +32139,15 @@
       <c r="A11" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="20"/>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
@@ -32174,7 +32168,7 @@
       <c r="Z11" s="4"/>
     </row>
     <row r="12" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="16" t="s">
         <v>43</v>
       </c>
       <c r="B12" s="5" t="s">
@@ -32189,11 +32183,11 @@
       <c r="E12" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F12" s="23" t="s">
+      <c r="F12" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="18"/>
-      <c r="H12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="20"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
@@ -32214,16 +32208,16 @@
       <c r="Z12" s="4"/>
     </row>
     <row r="13" spans="1:26" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="22"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="9" t="s">
         <v>70</v>
       </c>
       <c r="E13" s="5"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="19"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="20"/>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
@@ -32247,15 +32241,15 @@
       <c r="A14" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="25"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="24"/>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
@@ -32276,7 +32270,7 @@
       <c r="Z14" s="4"/>
     </row>
     <row r="15" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="16" t="s">
         <v>49</v>
       </c>
       <c r="B15" s="5" t="s">
@@ -32294,10 +32288,10 @@
       <c r="F15" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="G15" s="23" t="s">
+      <c r="G15" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="H15" s="19"/>
+      <c r="H15" s="20"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
@@ -32318,16 +32312,16 @@
       <c r="Z15" s="4"/>
     </row>
     <row r="16" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A16" s="22"/>
+      <c r="A16" s="17"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
       <c r="D16" s="8"/>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
-      <c r="G16" s="20" t="s">
+      <c r="G16" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="H16" s="19"/>
+      <c r="H16" s="20"/>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
@@ -32351,15 +32345,15 @@
       <c r="A17" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="28"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="12"/>
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
@@ -32383,15 +32377,15 @@
       <c r="A18" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="26" t="s">
+      <c r="B18" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="28"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="12"/>
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
@@ -32415,15 +32409,15 @@
       <c r="A19" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B19" s="26" t="s">
+      <c r="B19" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="28"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="12"/>
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
@@ -32447,15 +32441,15 @@
       <c r="A20" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B20" s="26" t="s">
+      <c r="B20" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="28"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="12"/>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
@@ -32476,7 +32470,7 @@
       <c r="Z20" s="4"/>
     </row>
     <row r="21" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="16" t="s">
         <v>59</v>
       </c>
       <c r="B21" s="5" t="s">
@@ -32520,7 +32514,7 @@
       <c r="Z21" s="4"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A22" s="22"/>
+      <c r="A22" s="17"/>
       <c r="B22" s="8" t="s">
         <v>70</v>
       </c>
@@ -32553,15 +32547,15 @@
       <c r="A23" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="20"/>
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
@@ -57111,6 +57105,16 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="B10:H10"/>
     <mergeCell ref="B23:H23"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A6:A7"/>
@@ -57127,16 +57131,6 @@
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="B14:H14"/>
     <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="B9:H9"/>
-    <mergeCell ref="B10:H10"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="F5:H5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B23" r:id="rId1" xr:uid="{97622EC6-5B10-4685-8838-BA744C09EBAD}"/>
@@ -57158,193 +57152,193 @@
     <col min="4" max="4" width="14.28515625" customWidth="1"/>
     <col min="5" max="5" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.140625" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
     <col min="8" max="8" width="26.5703125" customWidth="1"/>
     <col min="9" max="9" width="27.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A1" s="31" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="32" t="s">
         <v>147</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="32" t="s">
         <v>148</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="32" t="s">
         <v>150</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="32" t="s">
         <v>151</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="32" t="s">
         <v>152</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="32" t="s">
         <v>155</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="32" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="109.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="27" t="s">
         <v>162</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="27" t="s">
         <v>158</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="27" t="s">
         <v>159</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="27" t="s">
         <v>161</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="27" t="s">
         <v>160</v>
       </c>
-      <c r="H2" s="34" t="s">
+      <c r="H2" s="28" t="s">
         <v>186</v>
       </c>
-      <c r="I2" s="34" t="s">
+      <c r="I2" s="28" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="144" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="27" t="s">
         <v>172</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="27" t="s">
         <v>163</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="27" t="s">
         <v>157</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="27" t="s">
         <v>164</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="27" t="s">
         <v>166</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="27" t="s">
         <v>167</v>
       </c>
-      <c r="H3" s="35"/>
-      <c r="I3" s="35"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
     </row>
     <row r="4" spans="1:9" ht="201.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="27" t="s">
         <v>173</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="27" t="s">
         <v>168</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="27" t="s">
         <v>169</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="27" t="s">
         <v>170</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="27" t="s">
         <v>171</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="27" t="s">
         <v>167</v>
       </c>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
     </row>
     <row r="5" spans="1:9" ht="161.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="27" t="s">
         <v>174</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="27" t="s">
         <v>175</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="27" t="s">
         <v>167</v>
       </c>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
     </row>
     <row r="6" spans="1:9" ht="114.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="27" t="s">
         <v>178</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="27" t="s">
         <v>169</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="27" t="s">
         <v>180</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="27" t="s">
         <v>160</v>
       </c>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
     </row>
     <row r="7" spans="1:9" ht="111" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="27" t="s">
         <v>182</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="27" t="s">
         <v>183</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="27" t="s">
         <v>169</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="27" t="s">
         <v>184</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="27" t="s">
         <v>185</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="27" t="s">
         <v>160</v>
       </c>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="2">
